--- a/testing/glm-mv-reference/spss-output/mv4_posthoc.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv4_posthoc.xlsx
@@ -1336,115 +1336,115 @@
   </cellXfs>
   <cellStyles count="110">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1790219700919" xfId="1"/>
-    <cellStyle name="style1790219700986" xfId="2"/>
-    <cellStyle name="style1790219701005" xfId="3"/>
-    <cellStyle name="style1790219701042" xfId="4"/>
-    <cellStyle name="style1790219701066" xfId="5"/>
-    <cellStyle name="style1790219701103" xfId="6"/>
-    <cellStyle name="style1790219701125" xfId="7"/>
-    <cellStyle name="style1790219701156" xfId="8"/>
-    <cellStyle name="style1790219701174" xfId="9"/>
-    <cellStyle name="style1790219701212" xfId="10"/>
-    <cellStyle name="style1790219701236" xfId="11"/>
-    <cellStyle name="style1790219701271" xfId="12"/>
-    <cellStyle name="style1790219701297" xfId="13"/>
-    <cellStyle name="style1790219701328" xfId="14"/>
-    <cellStyle name="style1790219701350" xfId="15"/>
-    <cellStyle name="style1790219701377" xfId="16"/>
-    <cellStyle name="style1790219701394" xfId="17"/>
-    <cellStyle name="style1790219701420" xfId="18"/>
-    <cellStyle name="style1790219701440" xfId="19"/>
-    <cellStyle name="style1790219701471" xfId="20"/>
-    <cellStyle name="style1790219701496" xfId="21"/>
-    <cellStyle name="style1790219701522" xfId="22"/>
-    <cellStyle name="style1790219701540" xfId="23"/>
-    <cellStyle name="style1790219701560" xfId="24"/>
-    <cellStyle name="style1790219701577" xfId="25"/>
-    <cellStyle name="style1790219701597" xfId="26"/>
-    <cellStyle name="style1790219701627" xfId="27"/>
-    <cellStyle name="style1790219701648" xfId="28"/>
-    <cellStyle name="style1790219701676" xfId="29"/>
-    <cellStyle name="style1790219701692" xfId="30"/>
-    <cellStyle name="style1790219701724" xfId="31"/>
-    <cellStyle name="style1790219701751" xfId="32"/>
-    <cellStyle name="style1790219701772" xfId="33"/>
-    <cellStyle name="style1790219701791" xfId="34"/>
-    <cellStyle name="style1790219701819" xfId="35"/>
-    <cellStyle name="style1790219701848" xfId="36"/>
-    <cellStyle name="style1790219701866" xfId="37"/>
-    <cellStyle name="style1790219701890" xfId="38"/>
-    <cellStyle name="style1790219701909" xfId="39"/>
-    <cellStyle name="style1790219701935" xfId="40"/>
-    <cellStyle name="style1790219701958" xfId="41"/>
-    <cellStyle name="style1790219701984" xfId="42"/>
-    <cellStyle name="style1790219702008" xfId="43"/>
-    <cellStyle name="style1790219702027" xfId="44"/>
-    <cellStyle name="style1790219702051" xfId="45"/>
-    <cellStyle name="style1790219702069" xfId="46"/>
-    <cellStyle name="style1790219702087" xfId="47"/>
-    <cellStyle name="style1790219702103" xfId="48"/>
-    <cellStyle name="style1790219702118" xfId="49"/>
-    <cellStyle name="style1790219702134" xfId="50"/>
-    <cellStyle name="style1790219702150" xfId="51"/>
-    <cellStyle name="style1790219702167" xfId="52"/>
-    <cellStyle name="style1790219702199" xfId="53"/>
-    <cellStyle name="style1790219702213" xfId="54"/>
-    <cellStyle name="style1790219702229" xfId="55"/>
-    <cellStyle name="style1790219702260" xfId="56"/>
-    <cellStyle name="style1790219702288" xfId="57"/>
-    <cellStyle name="style1790219702306" xfId="58"/>
-    <cellStyle name="style1790219702326" xfId="59"/>
-    <cellStyle name="style1790219702345" xfId="60"/>
-    <cellStyle name="style1790219702359" xfId="61"/>
-    <cellStyle name="style1790219702379" xfId="62"/>
-    <cellStyle name="style1790219702397" xfId="63"/>
-    <cellStyle name="style1790219702415" xfId="64"/>
-    <cellStyle name="style1790219702419" xfId="65"/>
-    <cellStyle name="style1790219702435" xfId="66"/>
-    <cellStyle name="style1790219702467" xfId="67"/>
-    <cellStyle name="style1790219702482" xfId="68"/>
-    <cellStyle name="style1790219702498" xfId="69"/>
-    <cellStyle name="style1790219702533" xfId="70"/>
-    <cellStyle name="style1790219702552" xfId="71"/>
-    <cellStyle name="style1790219702567" xfId="72"/>
-    <cellStyle name="style1790219702590" xfId="73"/>
-    <cellStyle name="style1790219702608" xfId="74"/>
-    <cellStyle name="style1790219702636" xfId="75"/>
-    <cellStyle name="style1790219702652" xfId="76"/>
-    <cellStyle name="style1790219702674" xfId="77"/>
-    <cellStyle name="style1790219702686" xfId="78"/>
-    <cellStyle name="style1790219702707" xfId="79"/>
-    <cellStyle name="style1790219702723" xfId="80"/>
-    <cellStyle name="style1790219702733" xfId="81"/>
-    <cellStyle name="style1790219702750" xfId="82"/>
-    <cellStyle name="style1790219702774" xfId="83"/>
-    <cellStyle name="style1790219702795" xfId="84"/>
-    <cellStyle name="style1790219702813" xfId="85"/>
-    <cellStyle name="style1790219702829" xfId="86"/>
-    <cellStyle name="style1790219702845" xfId="87"/>
-    <cellStyle name="style1790219702874" xfId="88"/>
-    <cellStyle name="style1790219702892" xfId="89"/>
-    <cellStyle name="style1790219702913" xfId="90"/>
-    <cellStyle name="style1790219702939" xfId="91"/>
-    <cellStyle name="style1790219702961" xfId="92"/>
-    <cellStyle name="style1790219702982" xfId="93"/>
-    <cellStyle name="style1790219703008" xfId="94"/>
-    <cellStyle name="style1790219703029" xfId="95"/>
-    <cellStyle name="style1790219703049" xfId="96"/>
-    <cellStyle name="style1790219703076" xfId="97"/>
-    <cellStyle name="style1790219703096" xfId="98"/>
-    <cellStyle name="style1790219703124" xfId="99"/>
-    <cellStyle name="style1790219703163" xfId="100"/>
-    <cellStyle name="style1790219703189" xfId="101"/>
-    <cellStyle name="style1790219703204" xfId="102"/>
-    <cellStyle name="style1790219703222" xfId="103"/>
-    <cellStyle name="style1790219703241" xfId="104"/>
-    <cellStyle name="style1790219703257" xfId="105"/>
-    <cellStyle name="style1790219703275" xfId="106"/>
-    <cellStyle name="style1790219703285" xfId="107"/>
-    <cellStyle name="style1790219703324" xfId="108"/>
-    <cellStyle name="style1790219703343" xfId="109"/>
+    <cellStyle name="style1791033382648" xfId="1"/>
+    <cellStyle name="style1791033382695" xfId="2"/>
+    <cellStyle name="style1791033382720" xfId="3"/>
+    <cellStyle name="style1791033382752" xfId="4"/>
+    <cellStyle name="style1791033382785" xfId="5"/>
+    <cellStyle name="style1791033382819" xfId="6"/>
+    <cellStyle name="style1791033382840" xfId="7"/>
+    <cellStyle name="style1791033382871" xfId="8"/>
+    <cellStyle name="style1791033382902" xfId="9"/>
+    <cellStyle name="style1791033382923" xfId="10"/>
+    <cellStyle name="style1791033382954" xfId="11"/>
+    <cellStyle name="style1791033382985" xfId="12"/>
+    <cellStyle name="style1791033383017" xfId="13"/>
+    <cellStyle name="style1791033383048" xfId="14"/>
+    <cellStyle name="style1791033383079" xfId="15"/>
+    <cellStyle name="style1791033383099" xfId="16"/>
+    <cellStyle name="style1791033383120" xfId="17"/>
+    <cellStyle name="style1791033383142" xfId="18"/>
+    <cellStyle name="style1791033383174" xfId="19"/>
+    <cellStyle name="style1791033383193" xfId="20"/>
+    <cellStyle name="style1791033383220" xfId="21"/>
+    <cellStyle name="style1791033383246" xfId="22"/>
+    <cellStyle name="style1791033383267" xfId="23"/>
+    <cellStyle name="style1791033383287" xfId="24"/>
+    <cellStyle name="style1791033383309" xfId="25"/>
+    <cellStyle name="style1791033383331" xfId="26"/>
+    <cellStyle name="style1791033383363" xfId="27"/>
+    <cellStyle name="style1791033383381" xfId="28"/>
+    <cellStyle name="style1791033383412" xfId="29"/>
+    <cellStyle name="style1791033383437" xfId="30"/>
+    <cellStyle name="style1791033383458" xfId="31"/>
+    <cellStyle name="style1791033383485" xfId="32"/>
+    <cellStyle name="style1791033383509" xfId="33"/>
+    <cellStyle name="style1791033383538" xfId="34"/>
+    <cellStyle name="style1791033383557" xfId="35"/>
+    <cellStyle name="style1791033383592" xfId="36"/>
+    <cellStyle name="style1791033383608" xfId="37"/>
+    <cellStyle name="style1791033383633" xfId="38"/>
+    <cellStyle name="style1791033383650" xfId="39"/>
+    <cellStyle name="style1791033383676" xfId="40"/>
+    <cellStyle name="style1791033383703" xfId="41"/>
+    <cellStyle name="style1791033383722" xfId="42"/>
+    <cellStyle name="style1791033383751" xfId="43"/>
+    <cellStyle name="style1791033383768" xfId="44"/>
+    <cellStyle name="style1791033383795" xfId="45"/>
+    <cellStyle name="style1791033383810" xfId="46"/>
+    <cellStyle name="style1791033383829" xfId="47"/>
+    <cellStyle name="style1791033383847" xfId="48"/>
+    <cellStyle name="style1791033383857" xfId="49"/>
+    <cellStyle name="style1791033383878" xfId="50"/>
+    <cellStyle name="style1791033383899" xfId="51"/>
+    <cellStyle name="style1791033383920" xfId="52"/>
+    <cellStyle name="style1791033383941" xfId="53"/>
+    <cellStyle name="style1791033383952" xfId="54"/>
+    <cellStyle name="style1791033383983" xfId="55"/>
+    <cellStyle name="style1791033384004" xfId="56"/>
+    <cellStyle name="style1791033384031" xfId="57"/>
+    <cellStyle name="style1791033384053" xfId="58"/>
+    <cellStyle name="style1791033384071" xfId="59"/>
+    <cellStyle name="style1791033384088" xfId="60"/>
+    <cellStyle name="style1791033384109" xfId="61"/>
+    <cellStyle name="style1791033384128" xfId="62"/>
+    <cellStyle name="style1791033384147" xfId="63"/>
+    <cellStyle name="style1791033384164" xfId="64"/>
+    <cellStyle name="style1791033384175" xfId="65"/>
+    <cellStyle name="style1791033384197" xfId="66"/>
+    <cellStyle name="style1791033384213" xfId="67"/>
+    <cellStyle name="style1791033384235" xfId="68"/>
+    <cellStyle name="style1791033384252" xfId="69"/>
+    <cellStyle name="style1791033384283" xfId="70"/>
+    <cellStyle name="style1791033384299" xfId="71"/>
+    <cellStyle name="style1791033384319" xfId="72"/>
+    <cellStyle name="style1791033384330" xfId="73"/>
+    <cellStyle name="style1791033384350" xfId="74"/>
+    <cellStyle name="style1791033384382" xfId="75"/>
+    <cellStyle name="style1791033384399" xfId="76"/>
+    <cellStyle name="style1791033384414" xfId="77"/>
+    <cellStyle name="style1791033384434" xfId="78"/>
+    <cellStyle name="style1791033384446" xfId="79"/>
+    <cellStyle name="style1791033384465" xfId="80"/>
+    <cellStyle name="style1791033384486" xfId="81"/>
+    <cellStyle name="style1791033384504" xfId="82"/>
+    <cellStyle name="style1791033384520" xfId="83"/>
+    <cellStyle name="style1791033384539" xfId="84"/>
+    <cellStyle name="style1791033384560" xfId="85"/>
+    <cellStyle name="style1791033384581" xfId="86"/>
+    <cellStyle name="style1791033384604" xfId="87"/>
+    <cellStyle name="style1791033384618" xfId="88"/>
+    <cellStyle name="style1791033384633" xfId="89"/>
+    <cellStyle name="style1791033384664" xfId="90"/>
+    <cellStyle name="style1791033384685" xfId="91"/>
+    <cellStyle name="style1791033384706" xfId="92"/>
+    <cellStyle name="style1791033384728" xfId="93"/>
+    <cellStyle name="style1791033384748" xfId="94"/>
+    <cellStyle name="style1791033384775" xfId="95"/>
+    <cellStyle name="style1791033384800" xfId="96"/>
+    <cellStyle name="style1791033384822" xfId="97"/>
+    <cellStyle name="style1791033384845" xfId="98"/>
+    <cellStyle name="style1791033384869" xfId="99"/>
+    <cellStyle name="style1791033384906" xfId="100"/>
+    <cellStyle name="style1791033384938" xfId="101"/>
+    <cellStyle name="style1791033384955" xfId="102"/>
+    <cellStyle name="style1791033384969" xfId="103"/>
+    <cellStyle name="style1791033384990" xfId="104"/>
+    <cellStyle name="style1791033385009" xfId="105"/>
+    <cellStyle name="style1791033385025" xfId="106"/>
+    <cellStyle name="style1791033385044" xfId="107"/>
+    <cellStyle name="style1791033385084" xfId="108"/>
+    <cellStyle name="style1791033385100" xfId="109"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1856,7 +1856,7 @@
       <c r="B19" s="8"/>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>24-SEP-2026 10:15:00</t>
+          <t>03-OCT-2026 20:16:22</t>
         </is>
       </c>
     </row>

--- a/testing/glm-mv-reference/spss-output/mv4_posthoc.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv4_posthoc.xlsx
@@ -1336,115 +1336,115 @@
   </cellXfs>
   <cellStyles count="110">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1791033382648" xfId="1"/>
-    <cellStyle name="style1791033382695" xfId="2"/>
-    <cellStyle name="style1791033382720" xfId="3"/>
-    <cellStyle name="style1791033382752" xfId="4"/>
-    <cellStyle name="style1791033382785" xfId="5"/>
-    <cellStyle name="style1791033382819" xfId="6"/>
-    <cellStyle name="style1791033382840" xfId="7"/>
-    <cellStyle name="style1791033382871" xfId="8"/>
-    <cellStyle name="style1791033382902" xfId="9"/>
-    <cellStyle name="style1791033382923" xfId="10"/>
-    <cellStyle name="style1791033382954" xfId="11"/>
-    <cellStyle name="style1791033382985" xfId="12"/>
-    <cellStyle name="style1791033383017" xfId="13"/>
-    <cellStyle name="style1791033383048" xfId="14"/>
-    <cellStyle name="style1791033383079" xfId="15"/>
-    <cellStyle name="style1791033383099" xfId="16"/>
-    <cellStyle name="style1791033383120" xfId="17"/>
-    <cellStyle name="style1791033383142" xfId="18"/>
-    <cellStyle name="style1791033383174" xfId="19"/>
-    <cellStyle name="style1791033383193" xfId="20"/>
-    <cellStyle name="style1791033383220" xfId="21"/>
-    <cellStyle name="style1791033383246" xfId="22"/>
-    <cellStyle name="style1791033383267" xfId="23"/>
-    <cellStyle name="style1791033383287" xfId="24"/>
-    <cellStyle name="style1791033383309" xfId="25"/>
-    <cellStyle name="style1791033383331" xfId="26"/>
-    <cellStyle name="style1791033383363" xfId="27"/>
-    <cellStyle name="style1791033383381" xfId="28"/>
-    <cellStyle name="style1791033383412" xfId="29"/>
-    <cellStyle name="style1791033383437" xfId="30"/>
-    <cellStyle name="style1791033383458" xfId="31"/>
-    <cellStyle name="style1791033383485" xfId="32"/>
-    <cellStyle name="style1791033383509" xfId="33"/>
-    <cellStyle name="style1791033383538" xfId="34"/>
-    <cellStyle name="style1791033383557" xfId="35"/>
-    <cellStyle name="style1791033383592" xfId="36"/>
-    <cellStyle name="style1791033383608" xfId="37"/>
-    <cellStyle name="style1791033383633" xfId="38"/>
-    <cellStyle name="style1791033383650" xfId="39"/>
-    <cellStyle name="style1791033383676" xfId="40"/>
-    <cellStyle name="style1791033383703" xfId="41"/>
-    <cellStyle name="style1791033383722" xfId="42"/>
-    <cellStyle name="style1791033383751" xfId="43"/>
-    <cellStyle name="style1791033383768" xfId="44"/>
-    <cellStyle name="style1791033383795" xfId="45"/>
-    <cellStyle name="style1791033383810" xfId="46"/>
-    <cellStyle name="style1791033383829" xfId="47"/>
-    <cellStyle name="style1791033383847" xfId="48"/>
-    <cellStyle name="style1791033383857" xfId="49"/>
-    <cellStyle name="style1791033383878" xfId="50"/>
-    <cellStyle name="style1791033383899" xfId="51"/>
-    <cellStyle name="style1791033383920" xfId="52"/>
-    <cellStyle name="style1791033383941" xfId="53"/>
-    <cellStyle name="style1791033383952" xfId="54"/>
-    <cellStyle name="style1791033383983" xfId="55"/>
-    <cellStyle name="style1791033384004" xfId="56"/>
-    <cellStyle name="style1791033384031" xfId="57"/>
-    <cellStyle name="style1791033384053" xfId="58"/>
-    <cellStyle name="style1791033384071" xfId="59"/>
-    <cellStyle name="style1791033384088" xfId="60"/>
-    <cellStyle name="style1791033384109" xfId="61"/>
-    <cellStyle name="style1791033384128" xfId="62"/>
-    <cellStyle name="style1791033384147" xfId="63"/>
-    <cellStyle name="style1791033384164" xfId="64"/>
-    <cellStyle name="style1791033384175" xfId="65"/>
-    <cellStyle name="style1791033384197" xfId="66"/>
-    <cellStyle name="style1791033384213" xfId="67"/>
-    <cellStyle name="style1791033384235" xfId="68"/>
-    <cellStyle name="style1791033384252" xfId="69"/>
-    <cellStyle name="style1791033384283" xfId="70"/>
-    <cellStyle name="style1791033384299" xfId="71"/>
-    <cellStyle name="style1791033384319" xfId="72"/>
-    <cellStyle name="style1791033384330" xfId="73"/>
-    <cellStyle name="style1791033384350" xfId="74"/>
-    <cellStyle name="style1791033384382" xfId="75"/>
-    <cellStyle name="style1791033384399" xfId="76"/>
-    <cellStyle name="style1791033384414" xfId="77"/>
-    <cellStyle name="style1791033384434" xfId="78"/>
-    <cellStyle name="style1791033384446" xfId="79"/>
-    <cellStyle name="style1791033384465" xfId="80"/>
-    <cellStyle name="style1791033384486" xfId="81"/>
-    <cellStyle name="style1791033384504" xfId="82"/>
-    <cellStyle name="style1791033384520" xfId="83"/>
-    <cellStyle name="style1791033384539" xfId="84"/>
-    <cellStyle name="style1791033384560" xfId="85"/>
-    <cellStyle name="style1791033384581" xfId="86"/>
-    <cellStyle name="style1791033384604" xfId="87"/>
-    <cellStyle name="style1791033384618" xfId="88"/>
-    <cellStyle name="style1791033384633" xfId="89"/>
-    <cellStyle name="style1791033384664" xfId="90"/>
-    <cellStyle name="style1791033384685" xfId="91"/>
-    <cellStyle name="style1791033384706" xfId="92"/>
-    <cellStyle name="style1791033384728" xfId="93"/>
-    <cellStyle name="style1791033384748" xfId="94"/>
-    <cellStyle name="style1791033384775" xfId="95"/>
-    <cellStyle name="style1791033384800" xfId="96"/>
-    <cellStyle name="style1791033384822" xfId="97"/>
-    <cellStyle name="style1791033384845" xfId="98"/>
-    <cellStyle name="style1791033384869" xfId="99"/>
-    <cellStyle name="style1791033384906" xfId="100"/>
-    <cellStyle name="style1791033384938" xfId="101"/>
-    <cellStyle name="style1791033384955" xfId="102"/>
-    <cellStyle name="style1791033384969" xfId="103"/>
-    <cellStyle name="style1791033384990" xfId="104"/>
-    <cellStyle name="style1791033385009" xfId="105"/>
-    <cellStyle name="style1791033385025" xfId="106"/>
-    <cellStyle name="style1791033385044" xfId="107"/>
-    <cellStyle name="style1791033385084" xfId="108"/>
-    <cellStyle name="style1791033385100" xfId="109"/>
+    <cellStyle name="style1790219700919" xfId="1"/>
+    <cellStyle name="style1790219700986" xfId="2"/>
+    <cellStyle name="style1790219701005" xfId="3"/>
+    <cellStyle name="style1790219701042" xfId="4"/>
+    <cellStyle name="style1790219701066" xfId="5"/>
+    <cellStyle name="style1790219701103" xfId="6"/>
+    <cellStyle name="style1790219701125" xfId="7"/>
+    <cellStyle name="style1790219701156" xfId="8"/>
+    <cellStyle name="style1790219701174" xfId="9"/>
+    <cellStyle name="style1790219701212" xfId="10"/>
+    <cellStyle name="style1790219701236" xfId="11"/>
+    <cellStyle name="style1790219701271" xfId="12"/>
+    <cellStyle name="style1790219701297" xfId="13"/>
+    <cellStyle name="style1790219701328" xfId="14"/>
+    <cellStyle name="style1790219701350" xfId="15"/>
+    <cellStyle name="style1790219701377" xfId="16"/>
+    <cellStyle name="style1790219701394" xfId="17"/>
+    <cellStyle name="style1790219701420" xfId="18"/>
+    <cellStyle name="style1790219701440" xfId="19"/>
+    <cellStyle name="style1790219701471" xfId="20"/>
+    <cellStyle name="style1790219701496" xfId="21"/>
+    <cellStyle name="style1790219701522" xfId="22"/>
+    <cellStyle name="style1790219701540" xfId="23"/>
+    <cellStyle name="style1790219701560" xfId="24"/>
+    <cellStyle name="style1790219701577" xfId="25"/>
+    <cellStyle name="style1790219701597" xfId="26"/>
+    <cellStyle name="style1790219701627" xfId="27"/>
+    <cellStyle name="style1790219701648" xfId="28"/>
+    <cellStyle name="style1790219701676" xfId="29"/>
+    <cellStyle name="style1790219701692" xfId="30"/>
+    <cellStyle name="style1790219701724" xfId="31"/>
+    <cellStyle name="style1790219701751" xfId="32"/>
+    <cellStyle name="style1790219701772" xfId="33"/>
+    <cellStyle name="style1790219701791" xfId="34"/>
+    <cellStyle name="style1790219701819" xfId="35"/>
+    <cellStyle name="style1790219701848" xfId="36"/>
+    <cellStyle name="style1790219701866" xfId="37"/>
+    <cellStyle name="style1790219701890" xfId="38"/>
+    <cellStyle name="style1790219701909" xfId="39"/>
+    <cellStyle name="style1790219701935" xfId="40"/>
+    <cellStyle name="style1790219701958" xfId="41"/>
+    <cellStyle name="style1790219701984" xfId="42"/>
+    <cellStyle name="style1790219702008" xfId="43"/>
+    <cellStyle name="style1790219702027" xfId="44"/>
+    <cellStyle name="style1790219702051" xfId="45"/>
+    <cellStyle name="style1790219702069" xfId="46"/>
+    <cellStyle name="style1790219702087" xfId="47"/>
+    <cellStyle name="style1790219702103" xfId="48"/>
+    <cellStyle name="style1790219702118" xfId="49"/>
+    <cellStyle name="style1790219702134" xfId="50"/>
+    <cellStyle name="style1790219702150" xfId="51"/>
+    <cellStyle name="style1790219702167" xfId="52"/>
+    <cellStyle name="style1790219702199" xfId="53"/>
+    <cellStyle name="style1790219702213" xfId="54"/>
+    <cellStyle name="style1790219702229" xfId="55"/>
+    <cellStyle name="style1790219702260" xfId="56"/>
+    <cellStyle name="style1790219702288" xfId="57"/>
+    <cellStyle name="style1790219702306" xfId="58"/>
+    <cellStyle name="style1790219702326" xfId="59"/>
+    <cellStyle name="style1790219702345" xfId="60"/>
+    <cellStyle name="style1790219702359" xfId="61"/>
+    <cellStyle name="style1790219702379" xfId="62"/>
+    <cellStyle name="style1790219702397" xfId="63"/>
+    <cellStyle name="style1790219702415" xfId="64"/>
+    <cellStyle name="style1790219702419" xfId="65"/>
+    <cellStyle name="style1790219702435" xfId="66"/>
+    <cellStyle name="style1790219702467" xfId="67"/>
+    <cellStyle name="style1790219702482" xfId="68"/>
+    <cellStyle name="style1790219702498" xfId="69"/>
+    <cellStyle name="style1790219702533" xfId="70"/>
+    <cellStyle name="style1790219702552" xfId="71"/>
+    <cellStyle name="style1790219702567" xfId="72"/>
+    <cellStyle name="style1790219702590" xfId="73"/>
+    <cellStyle name="style1790219702608" xfId="74"/>
+    <cellStyle name="style1790219702636" xfId="75"/>
+    <cellStyle name="style1790219702652" xfId="76"/>
+    <cellStyle name="style1790219702674" xfId="77"/>
+    <cellStyle name="style1790219702686" xfId="78"/>
+    <cellStyle name="style1790219702707" xfId="79"/>
+    <cellStyle name="style1790219702723" xfId="80"/>
+    <cellStyle name="style1790219702733" xfId="81"/>
+    <cellStyle name="style1790219702750" xfId="82"/>
+    <cellStyle name="style1790219702774" xfId="83"/>
+    <cellStyle name="style1790219702795" xfId="84"/>
+    <cellStyle name="style1790219702813" xfId="85"/>
+    <cellStyle name="style1790219702829" xfId="86"/>
+    <cellStyle name="style1790219702845" xfId="87"/>
+    <cellStyle name="style1790219702874" xfId="88"/>
+    <cellStyle name="style1790219702892" xfId="89"/>
+    <cellStyle name="style1790219702913" xfId="90"/>
+    <cellStyle name="style1790219702939" xfId="91"/>
+    <cellStyle name="style1790219702961" xfId="92"/>
+    <cellStyle name="style1790219702982" xfId="93"/>
+    <cellStyle name="style1790219703008" xfId="94"/>
+    <cellStyle name="style1790219703029" xfId="95"/>
+    <cellStyle name="style1790219703049" xfId="96"/>
+    <cellStyle name="style1790219703076" xfId="97"/>
+    <cellStyle name="style1790219703096" xfId="98"/>
+    <cellStyle name="style1790219703124" xfId="99"/>
+    <cellStyle name="style1790219703163" xfId="100"/>
+    <cellStyle name="style1790219703189" xfId="101"/>
+    <cellStyle name="style1790219703204" xfId="102"/>
+    <cellStyle name="style1790219703222" xfId="103"/>
+    <cellStyle name="style1790219703241" xfId="104"/>
+    <cellStyle name="style1790219703257" xfId="105"/>
+    <cellStyle name="style1790219703275" xfId="106"/>
+    <cellStyle name="style1790219703285" xfId="107"/>
+    <cellStyle name="style1790219703324" xfId="108"/>
+    <cellStyle name="style1790219703343" xfId="109"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1856,7 +1856,7 @@
       <c r="B19" s="8"/>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>03-OCT-2026 20:16:22</t>
+          <t>24-SEP-2026 10:15:00</t>
         </is>
       </c>
     </row>
